--- a/Result/profitability/1530.xlsx
+++ b/Result/profitability/1530.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3675</v>
+        <v>0.2975</v>
       </c>
       <c r="N2" t="n">
-        <v>15.30375</v>
+        <v>14.8775</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4700000000000001</v>
+        <v>0.04625000000000004</v>
       </c>
       <c r="N3" t="n">
-        <v>17.2625</v>
+        <v>17.0025</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2437500000000001</v>
+        <v>0.6675000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>19.68375</v>
+        <v>19.0625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6950000000000001</v>
+        <v>0.785</v>
       </c>
       <c r="N5" t="n">
-        <v>20.44875</v>
+        <v>20.1275</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.79625</v>
+        <v>0.6375000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>21.9325</v>
+        <v>21.1675</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0.635</v>
+        <v>0.5925</v>
       </c>
       <c r="N7" t="n">
-        <v>23.1175</v>
+        <v>22.1925</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0.62625</v>
+        <v>0.6075</v>
       </c>
       <c r="N8" t="n">
-        <v>23.9775</v>
+        <v>23.51</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6050000000000001</v>
+        <v>0.605</v>
       </c>
       <c r="N9" t="n">
         <v>25.3175</v>
@@ -1899,7 +1899,7 @@
         <v>0.84</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3137500000000001</v>
+        <v>0.31375</v>
       </c>
       <c r="N12" t="n">
         <v>24.56375</v>
@@ -2026,7 +2026,7 @@
         <v>0.79</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3812500000000001</v>
+        <v>0.38125</v>
       </c>
       <c r="N13" t="n">
         <v>25.1925</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>468</v>
+      </c>
+      <c r="D75" t="n">
+        <v>425</v>
+      </c>
+      <c r="E75" t="n">
+        <v>42</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-39</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-8.35%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>35</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2300000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.83625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8333333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.739999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2924159499609068</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.043478260869565</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.569999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.221170395869191</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
